--- a/data/crime/PR_Crime_Summary_2010_2025.xlsx
+++ b/data/crime/PR_Crime_Summary_2010_2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/venettov/Documents/Capstone/CAPSTONE_DATA_SCIENCE_RIVERARUIZ/data/crime/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CED8081F-1982-2647-98E9-A038DCC593E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D851435F-3A25-C442-8F95-4F808BE47722}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="34560" windowHeight="21660" activeTab="3" xr2:uid="{43E4E03C-6A79-7E4D-A8F1-AF00C31A2DE9}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="34560" windowHeight="21660" xr2:uid="{43E4E03C-6A79-7E4D-A8F1-AF00C31A2DE9}"/>
   </bookViews>
   <sheets>
     <sheet name="2025" sheetId="1" r:id="rId1"/>
@@ -29,6 +29,7 @@
     <sheet name="2012" sheetId="15" r:id="rId14"/>
     <sheet name="2011" sheetId="16" r:id="rId15"/>
     <sheet name="2010" sheetId="17" r:id="rId16"/>
+    <sheet name="Legend" sheetId="19" r:id="rId17"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -51,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1429" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1460" uniqueCount="223">
   <si>
     <t>Totales</t>
   </si>
@@ -904,6 +905,194 @@
   <si>
     <t>Aguada</t>
   </si>
+  <si>
+    <t xml:space="preserve">1.  Asesinato y Homicidio Voluntario </t>
+  </si>
+  <si>
+    <r>
+      <t>Definición</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color indexed="8"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>- La muerte intencional (no negligente) de un ser humano por otro.</t>
+    </r>
+  </si>
+  <si>
+    <t>2.  Violación a la Fuerza</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Definición-  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color indexed="8"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>La cópula con una persona, a la fuerza y/o contra la voluntad de esa persona; o no a la</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve"> fuerza o contra la voluntad de la persona cuando la víctima es incapaz de dar su consentimiento</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> debido a su incapacidad mental o física temporal o permanente (o debido a su juventud.)</t>
+  </si>
+  <si>
+    <t>3.  Trata Humana</t>
+  </si>
+  <si>
+    <r>
+      <t>Definición-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color indexed="8"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> La captación, el traslado, el transporte, la acogida o la recepción de una persona</t>
+    </r>
+  </si>
+  <si>
+    <t>utilizando la violencia, la amenaza, el rapto, el abuso de poder u otros elementos de coacción</t>
+  </si>
+  <si>
+    <t>con el fin de someterla a la explotación sexual comercial o a la servidumbre involuntaria.</t>
+  </si>
+  <si>
+    <t>Con el propósito del lucro propio.</t>
+  </si>
+  <si>
+    <t>4.  Robo</t>
+  </si>
+  <si>
+    <r>
+      <t>Definición-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color indexed="8"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Llevarse o intentar llevarse cualquier cosa de valor, en circunstancias deconfrontación, </t>
+    </r>
+  </si>
+  <si>
+    <t>que se encuentra bajo el control, custodia o cuidado de otra  persona mediante la fuerza o amenaza</t>
+  </si>
+  <si>
+    <t>de fuerza o violencia y/o poner a la víctima  en temor de daño inmediato.</t>
+  </si>
+  <si>
+    <t>5.  Agresión Grave</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Definición – </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color indexed="8"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Un ataque ilícito de una persona contra otra en la cual el agresor utiliza un arma o la</t>
+    </r>
+  </si>
+  <si>
+    <t>exhibe de manera amenazadora, o la víctima sufre una lesión corporal severa o grave, incluyendo</t>
+  </si>
+  <si>
+    <t>huesos fracturados, pérdida de dientes, posibles lesiones internas, desgarraduras severas o  pérdida</t>
+  </si>
+  <si>
+    <t xml:space="preserve">de conocimiento aparentes. </t>
+  </si>
+  <si>
+    <t>6.  Escalamiento/Allanamiento de Morada</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13"/>
+        <color indexed="8"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Definición –</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color indexed="8"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> La entrada ilícita a un edificio u otra estructura con la intención de cometer un delito</t>
+    </r>
+  </si>
+  <si>
+    <t>mayor o un robo.</t>
+  </si>
+  <si>
+    <t>7.  Apropiación Ilegal</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Definición- </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color indexed="8"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Adquirir, transportar, llevar o montarse en y llevarse bienes que le pertenecen real o </t>
+    </r>
+  </si>
+  <si>
+    <t>legalmente a otra persona.</t>
+  </si>
+  <si>
+    <t>8.  Hurto de Auto</t>
+  </si>
+  <si>
+    <r>
+      <t>Definición</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color indexed="8"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>- El hurto de un vehículo de motor.</t>
+    </r>
+  </si>
+  <si>
+    <t>Se deben clasificar como hurto de auto de vehículos de motor todos los casos en que las personas que</t>
+  </si>
+  <si>
+    <t xml:space="preserve">personas que no tienen acceso legal a automóviles se los llevan y posteriormente los abandonan. </t>
+  </si>
+  <si>
+    <t>Se debe incluir el llevarse un vehículo sin permiso del dueño para realizar paseos alocados.</t>
+  </si>
 </sst>
 </file>
 
@@ -912,7 +1101,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -966,6 +1155,56 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="13"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color indexed="8"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color indexed="8"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -984,11 +1223,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1045,9 +1285,36 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{790BE479-562B-B641-B0D7-C08311E4472D}"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -21600,6 +21867,898 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77629FE4-0AAF-4F45-8D35-1C3005808586}">
+  <dimension ref="A2:J46"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="17" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="13.5" style="22" customWidth="1"/>
+    <col min="2" max="8" width="9.1640625" style="22"/>
+    <col min="9" max="9" width="27" style="22" customWidth="1"/>
+    <col min="10" max="10" width="11.33203125" style="22" customWidth="1"/>
+    <col min="11" max="256" width="9.1640625" style="22"/>
+    <col min="257" max="257" width="13.5" style="22" customWidth="1"/>
+    <col min="258" max="264" width="9.1640625" style="22"/>
+    <col min="265" max="265" width="27" style="22" customWidth="1"/>
+    <col min="266" max="266" width="11.33203125" style="22" customWidth="1"/>
+    <col min="267" max="512" width="9.1640625" style="22"/>
+    <col min="513" max="513" width="13.5" style="22" customWidth="1"/>
+    <col min="514" max="520" width="9.1640625" style="22"/>
+    <col min="521" max="521" width="27" style="22" customWidth="1"/>
+    <col min="522" max="522" width="11.33203125" style="22" customWidth="1"/>
+    <col min="523" max="768" width="9.1640625" style="22"/>
+    <col min="769" max="769" width="13.5" style="22" customWidth="1"/>
+    <col min="770" max="776" width="9.1640625" style="22"/>
+    <col min="777" max="777" width="27" style="22" customWidth="1"/>
+    <col min="778" max="778" width="11.33203125" style="22" customWidth="1"/>
+    <col min="779" max="1024" width="9.1640625" style="22"/>
+    <col min="1025" max="1025" width="13.5" style="22" customWidth="1"/>
+    <col min="1026" max="1032" width="9.1640625" style="22"/>
+    <col min="1033" max="1033" width="27" style="22" customWidth="1"/>
+    <col min="1034" max="1034" width="11.33203125" style="22" customWidth="1"/>
+    <col min="1035" max="1280" width="9.1640625" style="22"/>
+    <col min="1281" max="1281" width="13.5" style="22" customWidth="1"/>
+    <col min="1282" max="1288" width="9.1640625" style="22"/>
+    <col min="1289" max="1289" width="27" style="22" customWidth="1"/>
+    <col min="1290" max="1290" width="11.33203125" style="22" customWidth="1"/>
+    <col min="1291" max="1536" width="9.1640625" style="22"/>
+    <col min="1537" max="1537" width="13.5" style="22" customWidth="1"/>
+    <col min="1538" max="1544" width="9.1640625" style="22"/>
+    <col min="1545" max="1545" width="27" style="22" customWidth="1"/>
+    <col min="1546" max="1546" width="11.33203125" style="22" customWidth="1"/>
+    <col min="1547" max="1792" width="9.1640625" style="22"/>
+    <col min="1793" max="1793" width="13.5" style="22" customWidth="1"/>
+    <col min="1794" max="1800" width="9.1640625" style="22"/>
+    <col min="1801" max="1801" width="27" style="22" customWidth="1"/>
+    <col min="1802" max="1802" width="11.33203125" style="22" customWidth="1"/>
+    <col min="1803" max="2048" width="9.1640625" style="22"/>
+    <col min="2049" max="2049" width="13.5" style="22" customWidth="1"/>
+    <col min="2050" max="2056" width="9.1640625" style="22"/>
+    <col min="2057" max="2057" width="27" style="22" customWidth="1"/>
+    <col min="2058" max="2058" width="11.33203125" style="22" customWidth="1"/>
+    <col min="2059" max="2304" width="9.1640625" style="22"/>
+    <col min="2305" max="2305" width="13.5" style="22" customWidth="1"/>
+    <col min="2306" max="2312" width="9.1640625" style="22"/>
+    <col min="2313" max="2313" width="27" style="22" customWidth="1"/>
+    <col min="2314" max="2314" width="11.33203125" style="22" customWidth="1"/>
+    <col min="2315" max="2560" width="9.1640625" style="22"/>
+    <col min="2561" max="2561" width="13.5" style="22" customWidth="1"/>
+    <col min="2562" max="2568" width="9.1640625" style="22"/>
+    <col min="2569" max="2569" width="27" style="22" customWidth="1"/>
+    <col min="2570" max="2570" width="11.33203125" style="22" customWidth="1"/>
+    <col min="2571" max="2816" width="9.1640625" style="22"/>
+    <col min="2817" max="2817" width="13.5" style="22" customWidth="1"/>
+    <col min="2818" max="2824" width="9.1640625" style="22"/>
+    <col min="2825" max="2825" width="27" style="22" customWidth="1"/>
+    <col min="2826" max="2826" width="11.33203125" style="22" customWidth="1"/>
+    <col min="2827" max="3072" width="9.1640625" style="22"/>
+    <col min="3073" max="3073" width="13.5" style="22" customWidth="1"/>
+    <col min="3074" max="3080" width="9.1640625" style="22"/>
+    <col min="3081" max="3081" width="27" style="22" customWidth="1"/>
+    <col min="3082" max="3082" width="11.33203125" style="22" customWidth="1"/>
+    <col min="3083" max="3328" width="9.1640625" style="22"/>
+    <col min="3329" max="3329" width="13.5" style="22" customWidth="1"/>
+    <col min="3330" max="3336" width="9.1640625" style="22"/>
+    <col min="3337" max="3337" width="27" style="22" customWidth="1"/>
+    <col min="3338" max="3338" width="11.33203125" style="22" customWidth="1"/>
+    <col min="3339" max="3584" width="9.1640625" style="22"/>
+    <col min="3585" max="3585" width="13.5" style="22" customWidth="1"/>
+    <col min="3586" max="3592" width="9.1640625" style="22"/>
+    <col min="3593" max="3593" width="27" style="22" customWidth="1"/>
+    <col min="3594" max="3594" width="11.33203125" style="22" customWidth="1"/>
+    <col min="3595" max="3840" width="9.1640625" style="22"/>
+    <col min="3841" max="3841" width="13.5" style="22" customWidth="1"/>
+    <col min="3842" max="3848" width="9.1640625" style="22"/>
+    <col min="3849" max="3849" width="27" style="22" customWidth="1"/>
+    <col min="3850" max="3850" width="11.33203125" style="22" customWidth="1"/>
+    <col min="3851" max="4096" width="9.1640625" style="22"/>
+    <col min="4097" max="4097" width="13.5" style="22" customWidth="1"/>
+    <col min="4098" max="4104" width="9.1640625" style="22"/>
+    <col min="4105" max="4105" width="27" style="22" customWidth="1"/>
+    <col min="4106" max="4106" width="11.33203125" style="22" customWidth="1"/>
+    <col min="4107" max="4352" width="9.1640625" style="22"/>
+    <col min="4353" max="4353" width="13.5" style="22" customWidth="1"/>
+    <col min="4354" max="4360" width="9.1640625" style="22"/>
+    <col min="4361" max="4361" width="27" style="22" customWidth="1"/>
+    <col min="4362" max="4362" width="11.33203125" style="22" customWidth="1"/>
+    <col min="4363" max="4608" width="9.1640625" style="22"/>
+    <col min="4609" max="4609" width="13.5" style="22" customWidth="1"/>
+    <col min="4610" max="4616" width="9.1640625" style="22"/>
+    <col min="4617" max="4617" width="27" style="22" customWidth="1"/>
+    <col min="4618" max="4618" width="11.33203125" style="22" customWidth="1"/>
+    <col min="4619" max="4864" width="9.1640625" style="22"/>
+    <col min="4865" max="4865" width="13.5" style="22" customWidth="1"/>
+    <col min="4866" max="4872" width="9.1640625" style="22"/>
+    <col min="4873" max="4873" width="27" style="22" customWidth="1"/>
+    <col min="4874" max="4874" width="11.33203125" style="22" customWidth="1"/>
+    <col min="4875" max="5120" width="9.1640625" style="22"/>
+    <col min="5121" max="5121" width="13.5" style="22" customWidth="1"/>
+    <col min="5122" max="5128" width="9.1640625" style="22"/>
+    <col min="5129" max="5129" width="27" style="22" customWidth="1"/>
+    <col min="5130" max="5130" width="11.33203125" style="22" customWidth="1"/>
+    <col min="5131" max="5376" width="9.1640625" style="22"/>
+    <col min="5377" max="5377" width="13.5" style="22" customWidth="1"/>
+    <col min="5378" max="5384" width="9.1640625" style="22"/>
+    <col min="5385" max="5385" width="27" style="22" customWidth="1"/>
+    <col min="5386" max="5386" width="11.33203125" style="22" customWidth="1"/>
+    <col min="5387" max="5632" width="9.1640625" style="22"/>
+    <col min="5633" max="5633" width="13.5" style="22" customWidth="1"/>
+    <col min="5634" max="5640" width="9.1640625" style="22"/>
+    <col min="5641" max="5641" width="27" style="22" customWidth="1"/>
+    <col min="5642" max="5642" width="11.33203125" style="22" customWidth="1"/>
+    <col min="5643" max="5888" width="9.1640625" style="22"/>
+    <col min="5889" max="5889" width="13.5" style="22" customWidth="1"/>
+    <col min="5890" max="5896" width="9.1640625" style="22"/>
+    <col min="5897" max="5897" width="27" style="22" customWidth="1"/>
+    <col min="5898" max="5898" width="11.33203125" style="22" customWidth="1"/>
+    <col min="5899" max="6144" width="9.1640625" style="22"/>
+    <col min="6145" max="6145" width="13.5" style="22" customWidth="1"/>
+    <col min="6146" max="6152" width="9.1640625" style="22"/>
+    <col min="6153" max="6153" width="27" style="22" customWidth="1"/>
+    <col min="6154" max="6154" width="11.33203125" style="22" customWidth="1"/>
+    <col min="6155" max="6400" width="9.1640625" style="22"/>
+    <col min="6401" max="6401" width="13.5" style="22" customWidth="1"/>
+    <col min="6402" max="6408" width="9.1640625" style="22"/>
+    <col min="6409" max="6409" width="27" style="22" customWidth="1"/>
+    <col min="6410" max="6410" width="11.33203125" style="22" customWidth="1"/>
+    <col min="6411" max="6656" width="9.1640625" style="22"/>
+    <col min="6657" max="6657" width="13.5" style="22" customWidth="1"/>
+    <col min="6658" max="6664" width="9.1640625" style="22"/>
+    <col min="6665" max="6665" width="27" style="22" customWidth="1"/>
+    <col min="6666" max="6666" width="11.33203125" style="22" customWidth="1"/>
+    <col min="6667" max="6912" width="9.1640625" style="22"/>
+    <col min="6913" max="6913" width="13.5" style="22" customWidth="1"/>
+    <col min="6914" max="6920" width="9.1640625" style="22"/>
+    <col min="6921" max="6921" width="27" style="22" customWidth="1"/>
+    <col min="6922" max="6922" width="11.33203125" style="22" customWidth="1"/>
+    <col min="6923" max="7168" width="9.1640625" style="22"/>
+    <col min="7169" max="7169" width="13.5" style="22" customWidth="1"/>
+    <col min="7170" max="7176" width="9.1640625" style="22"/>
+    <col min="7177" max="7177" width="27" style="22" customWidth="1"/>
+    <col min="7178" max="7178" width="11.33203125" style="22" customWidth="1"/>
+    <col min="7179" max="7424" width="9.1640625" style="22"/>
+    <col min="7425" max="7425" width="13.5" style="22" customWidth="1"/>
+    <col min="7426" max="7432" width="9.1640625" style="22"/>
+    <col min="7433" max="7433" width="27" style="22" customWidth="1"/>
+    <col min="7434" max="7434" width="11.33203125" style="22" customWidth="1"/>
+    <col min="7435" max="7680" width="9.1640625" style="22"/>
+    <col min="7681" max="7681" width="13.5" style="22" customWidth="1"/>
+    <col min="7682" max="7688" width="9.1640625" style="22"/>
+    <col min="7689" max="7689" width="27" style="22" customWidth="1"/>
+    <col min="7690" max="7690" width="11.33203125" style="22" customWidth="1"/>
+    <col min="7691" max="7936" width="9.1640625" style="22"/>
+    <col min="7937" max="7937" width="13.5" style="22" customWidth="1"/>
+    <col min="7938" max="7944" width="9.1640625" style="22"/>
+    <col min="7945" max="7945" width="27" style="22" customWidth="1"/>
+    <col min="7946" max="7946" width="11.33203125" style="22" customWidth="1"/>
+    <col min="7947" max="8192" width="9.1640625" style="22"/>
+    <col min="8193" max="8193" width="13.5" style="22" customWidth="1"/>
+    <col min="8194" max="8200" width="9.1640625" style="22"/>
+    <col min="8201" max="8201" width="27" style="22" customWidth="1"/>
+    <col min="8202" max="8202" width="11.33203125" style="22" customWidth="1"/>
+    <col min="8203" max="8448" width="9.1640625" style="22"/>
+    <col min="8449" max="8449" width="13.5" style="22" customWidth="1"/>
+    <col min="8450" max="8456" width="9.1640625" style="22"/>
+    <col min="8457" max="8457" width="27" style="22" customWidth="1"/>
+    <col min="8458" max="8458" width="11.33203125" style="22" customWidth="1"/>
+    <col min="8459" max="8704" width="9.1640625" style="22"/>
+    <col min="8705" max="8705" width="13.5" style="22" customWidth="1"/>
+    <col min="8706" max="8712" width="9.1640625" style="22"/>
+    <col min="8713" max="8713" width="27" style="22" customWidth="1"/>
+    <col min="8714" max="8714" width="11.33203125" style="22" customWidth="1"/>
+    <col min="8715" max="8960" width="9.1640625" style="22"/>
+    <col min="8961" max="8961" width="13.5" style="22" customWidth="1"/>
+    <col min="8962" max="8968" width="9.1640625" style="22"/>
+    <col min="8969" max="8969" width="27" style="22" customWidth="1"/>
+    <col min="8970" max="8970" width="11.33203125" style="22" customWidth="1"/>
+    <col min="8971" max="9216" width="9.1640625" style="22"/>
+    <col min="9217" max="9217" width="13.5" style="22" customWidth="1"/>
+    <col min="9218" max="9224" width="9.1640625" style="22"/>
+    <col min="9225" max="9225" width="27" style="22" customWidth="1"/>
+    <col min="9226" max="9226" width="11.33203125" style="22" customWidth="1"/>
+    <col min="9227" max="9472" width="9.1640625" style="22"/>
+    <col min="9473" max="9473" width="13.5" style="22" customWidth="1"/>
+    <col min="9474" max="9480" width="9.1640625" style="22"/>
+    <col min="9481" max="9481" width="27" style="22" customWidth="1"/>
+    <col min="9482" max="9482" width="11.33203125" style="22" customWidth="1"/>
+    <col min="9483" max="9728" width="9.1640625" style="22"/>
+    <col min="9729" max="9729" width="13.5" style="22" customWidth="1"/>
+    <col min="9730" max="9736" width="9.1640625" style="22"/>
+    <col min="9737" max="9737" width="27" style="22" customWidth="1"/>
+    <col min="9738" max="9738" width="11.33203125" style="22" customWidth="1"/>
+    <col min="9739" max="9984" width="9.1640625" style="22"/>
+    <col min="9985" max="9985" width="13.5" style="22" customWidth="1"/>
+    <col min="9986" max="9992" width="9.1640625" style="22"/>
+    <col min="9993" max="9993" width="27" style="22" customWidth="1"/>
+    <col min="9994" max="9994" width="11.33203125" style="22" customWidth="1"/>
+    <col min="9995" max="10240" width="9.1640625" style="22"/>
+    <col min="10241" max="10241" width="13.5" style="22" customWidth="1"/>
+    <col min="10242" max="10248" width="9.1640625" style="22"/>
+    <col min="10249" max="10249" width="27" style="22" customWidth="1"/>
+    <col min="10250" max="10250" width="11.33203125" style="22" customWidth="1"/>
+    <col min="10251" max="10496" width="9.1640625" style="22"/>
+    <col min="10497" max="10497" width="13.5" style="22" customWidth="1"/>
+    <col min="10498" max="10504" width="9.1640625" style="22"/>
+    <col min="10505" max="10505" width="27" style="22" customWidth="1"/>
+    <col min="10506" max="10506" width="11.33203125" style="22" customWidth="1"/>
+    <col min="10507" max="10752" width="9.1640625" style="22"/>
+    <col min="10753" max="10753" width="13.5" style="22" customWidth="1"/>
+    <col min="10754" max="10760" width="9.1640625" style="22"/>
+    <col min="10761" max="10761" width="27" style="22" customWidth="1"/>
+    <col min="10762" max="10762" width="11.33203125" style="22" customWidth="1"/>
+    <col min="10763" max="11008" width="9.1640625" style="22"/>
+    <col min="11009" max="11009" width="13.5" style="22" customWidth="1"/>
+    <col min="11010" max="11016" width="9.1640625" style="22"/>
+    <col min="11017" max="11017" width="27" style="22" customWidth="1"/>
+    <col min="11018" max="11018" width="11.33203125" style="22" customWidth="1"/>
+    <col min="11019" max="11264" width="9.1640625" style="22"/>
+    <col min="11265" max="11265" width="13.5" style="22" customWidth="1"/>
+    <col min="11266" max="11272" width="9.1640625" style="22"/>
+    <col min="11273" max="11273" width="27" style="22" customWidth="1"/>
+    <col min="11274" max="11274" width="11.33203125" style="22" customWidth="1"/>
+    <col min="11275" max="11520" width="9.1640625" style="22"/>
+    <col min="11521" max="11521" width="13.5" style="22" customWidth="1"/>
+    <col min="11522" max="11528" width="9.1640625" style="22"/>
+    <col min="11529" max="11529" width="27" style="22" customWidth="1"/>
+    <col min="11530" max="11530" width="11.33203125" style="22" customWidth="1"/>
+    <col min="11531" max="11776" width="9.1640625" style="22"/>
+    <col min="11777" max="11777" width="13.5" style="22" customWidth="1"/>
+    <col min="11778" max="11784" width="9.1640625" style="22"/>
+    <col min="11785" max="11785" width="27" style="22" customWidth="1"/>
+    <col min="11786" max="11786" width="11.33203125" style="22" customWidth="1"/>
+    <col min="11787" max="12032" width="9.1640625" style="22"/>
+    <col min="12033" max="12033" width="13.5" style="22" customWidth="1"/>
+    <col min="12034" max="12040" width="9.1640625" style="22"/>
+    <col min="12041" max="12041" width="27" style="22" customWidth="1"/>
+    <col min="12042" max="12042" width="11.33203125" style="22" customWidth="1"/>
+    <col min="12043" max="12288" width="9.1640625" style="22"/>
+    <col min="12289" max="12289" width="13.5" style="22" customWidth="1"/>
+    <col min="12290" max="12296" width="9.1640625" style="22"/>
+    <col min="12297" max="12297" width="27" style="22" customWidth="1"/>
+    <col min="12298" max="12298" width="11.33203125" style="22" customWidth="1"/>
+    <col min="12299" max="12544" width="9.1640625" style="22"/>
+    <col min="12545" max="12545" width="13.5" style="22" customWidth="1"/>
+    <col min="12546" max="12552" width="9.1640625" style="22"/>
+    <col min="12553" max="12553" width="27" style="22" customWidth="1"/>
+    <col min="12554" max="12554" width="11.33203125" style="22" customWidth="1"/>
+    <col min="12555" max="12800" width="9.1640625" style="22"/>
+    <col min="12801" max="12801" width="13.5" style="22" customWidth="1"/>
+    <col min="12802" max="12808" width="9.1640625" style="22"/>
+    <col min="12809" max="12809" width="27" style="22" customWidth="1"/>
+    <col min="12810" max="12810" width="11.33203125" style="22" customWidth="1"/>
+    <col min="12811" max="13056" width="9.1640625" style="22"/>
+    <col min="13057" max="13057" width="13.5" style="22" customWidth="1"/>
+    <col min="13058" max="13064" width="9.1640625" style="22"/>
+    <col min="13065" max="13065" width="27" style="22" customWidth="1"/>
+    <col min="13066" max="13066" width="11.33203125" style="22" customWidth="1"/>
+    <col min="13067" max="13312" width="9.1640625" style="22"/>
+    <col min="13313" max="13313" width="13.5" style="22" customWidth="1"/>
+    <col min="13314" max="13320" width="9.1640625" style="22"/>
+    <col min="13321" max="13321" width="27" style="22" customWidth="1"/>
+    <col min="13322" max="13322" width="11.33203125" style="22" customWidth="1"/>
+    <col min="13323" max="13568" width="9.1640625" style="22"/>
+    <col min="13569" max="13569" width="13.5" style="22" customWidth="1"/>
+    <col min="13570" max="13576" width="9.1640625" style="22"/>
+    <col min="13577" max="13577" width="27" style="22" customWidth="1"/>
+    <col min="13578" max="13578" width="11.33203125" style="22" customWidth="1"/>
+    <col min="13579" max="13824" width="9.1640625" style="22"/>
+    <col min="13825" max="13825" width="13.5" style="22" customWidth="1"/>
+    <col min="13826" max="13832" width="9.1640625" style="22"/>
+    <col min="13833" max="13833" width="27" style="22" customWidth="1"/>
+    <col min="13834" max="13834" width="11.33203125" style="22" customWidth="1"/>
+    <col min="13835" max="14080" width="9.1640625" style="22"/>
+    <col min="14081" max="14081" width="13.5" style="22" customWidth="1"/>
+    <col min="14082" max="14088" width="9.1640625" style="22"/>
+    <col min="14089" max="14089" width="27" style="22" customWidth="1"/>
+    <col min="14090" max="14090" width="11.33203125" style="22" customWidth="1"/>
+    <col min="14091" max="14336" width="9.1640625" style="22"/>
+    <col min="14337" max="14337" width="13.5" style="22" customWidth="1"/>
+    <col min="14338" max="14344" width="9.1640625" style="22"/>
+    <col min="14345" max="14345" width="27" style="22" customWidth="1"/>
+    <col min="14346" max="14346" width="11.33203125" style="22" customWidth="1"/>
+    <col min="14347" max="14592" width="9.1640625" style="22"/>
+    <col min="14593" max="14593" width="13.5" style="22" customWidth="1"/>
+    <col min="14594" max="14600" width="9.1640625" style="22"/>
+    <col min="14601" max="14601" width="27" style="22" customWidth="1"/>
+    <col min="14602" max="14602" width="11.33203125" style="22" customWidth="1"/>
+    <col min="14603" max="14848" width="9.1640625" style="22"/>
+    <col min="14849" max="14849" width="13.5" style="22" customWidth="1"/>
+    <col min="14850" max="14856" width="9.1640625" style="22"/>
+    <col min="14857" max="14857" width="27" style="22" customWidth="1"/>
+    <col min="14858" max="14858" width="11.33203125" style="22" customWidth="1"/>
+    <col min="14859" max="15104" width="9.1640625" style="22"/>
+    <col min="15105" max="15105" width="13.5" style="22" customWidth="1"/>
+    <col min="15106" max="15112" width="9.1640625" style="22"/>
+    <col min="15113" max="15113" width="27" style="22" customWidth="1"/>
+    <col min="15114" max="15114" width="11.33203125" style="22" customWidth="1"/>
+    <col min="15115" max="15360" width="9.1640625" style="22"/>
+    <col min="15361" max="15361" width="13.5" style="22" customWidth="1"/>
+    <col min="15362" max="15368" width="9.1640625" style="22"/>
+    <col min="15369" max="15369" width="27" style="22" customWidth="1"/>
+    <col min="15370" max="15370" width="11.33203125" style="22" customWidth="1"/>
+    <col min="15371" max="15616" width="9.1640625" style="22"/>
+    <col min="15617" max="15617" width="13.5" style="22" customWidth="1"/>
+    <col min="15618" max="15624" width="9.1640625" style="22"/>
+    <col min="15625" max="15625" width="27" style="22" customWidth="1"/>
+    <col min="15626" max="15626" width="11.33203125" style="22" customWidth="1"/>
+    <col min="15627" max="15872" width="9.1640625" style="22"/>
+    <col min="15873" max="15873" width="13.5" style="22" customWidth="1"/>
+    <col min="15874" max="15880" width="9.1640625" style="22"/>
+    <col min="15881" max="15881" width="27" style="22" customWidth="1"/>
+    <col min="15882" max="15882" width="11.33203125" style="22" customWidth="1"/>
+    <col min="15883" max="16128" width="9.1640625" style="22"/>
+    <col min="16129" max="16129" width="13.5" style="22" customWidth="1"/>
+    <col min="16130" max="16136" width="9.1640625" style="22"/>
+    <col min="16137" max="16137" width="27" style="22" customWidth="1"/>
+    <col min="16138" max="16138" width="11.33203125" style="22" customWidth="1"/>
+    <col min="16139" max="16384" width="9.1640625" style="22"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+      <c r="A2" s="23" t="s">
+        <v>192</v>
+      </c>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
+    </row>
+    <row r="3" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+      <c r="A3" s="24"/>
+      <c r="B3" s="23" t="s">
+        <v>193</v>
+      </c>
+      <c r="C3" s="23"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="23"/>
+      <c r="H3" s="23"/>
+      <c r="I3" s="23"/>
+    </row>
+    <row r="4" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+      <c r="A4" s="24"/>
+      <c r="B4" s="25"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="25"/>
+      <c r="I4" s="25"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A6" s="23" t="s">
+        <v>194</v>
+      </c>
+      <c r="B6" s="23"/>
+      <c r="C6" s="23"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A7" s="25"/>
+      <c r="B7" s="23" t="s">
+        <v>195</v>
+      </c>
+      <c r="C7" s="23"/>
+      <c r="D7" s="23"/>
+      <c r="E7" s="23"/>
+      <c r="F7" s="23"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="23"/>
+      <c r="I7" s="23"/>
+      <c r="J7" s="23"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A8" s="25"/>
+      <c r="B8" s="26" t="s">
+        <v>196</v>
+      </c>
+      <c r="C8" s="26"/>
+      <c r="D8" s="26"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="26"/>
+      <c r="H8" s="26"/>
+      <c r="I8" s="26"/>
+      <c r="J8" s="26"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A9" s="25"/>
+      <c r="B9" s="26" t="s">
+        <v>197</v>
+      </c>
+      <c r="C9" s="26"/>
+      <c r="D9" s="26"/>
+      <c r="E9" s="26"/>
+      <c r="F9" s="26"/>
+      <c r="G9" s="26"/>
+      <c r="H9" s="26"/>
+      <c r="I9" s="26"/>
+      <c r="J9" s="26"/>
+    </row>
+    <row r="10" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+      <c r="A10" s="24"/>
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
+      <c r="G10" s="27"/>
+      <c r="H10" s="27"/>
+      <c r="I10" s="27"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A11" s="25" t="s">
+        <v>198</v>
+      </c>
+      <c r="B11" s="25"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="27"/>
+      <c r="G11" s="27"/>
+      <c r="H11" s="27"/>
+      <c r="I11" s="27"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A12" s="28"/>
+      <c r="B12" s="25" t="s">
+        <v>199</v>
+      </c>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="28"/>
+      <c r="F12" s="28"/>
+      <c r="G12" s="28"/>
+      <c r="H12" s="28"/>
+      <c r="I12" s="28"/>
+      <c r="J12" s="28"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A13" s="25"/>
+      <c r="B13" s="28" t="s">
+        <v>200</v>
+      </c>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="28"/>
+      <c r="H13" s="28"/>
+      <c r="I13" s="28"/>
+      <c r="J13" s="28"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A14" s="25"/>
+      <c r="B14" s="28" t="s">
+        <v>201</v>
+      </c>
+      <c r="C14" s="28"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="28"/>
+      <c r="G14" s="28"/>
+      <c r="H14" s="28"/>
+      <c r="I14" s="28"/>
+      <c r="J14" s="28"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B15" s="29" t="s">
+        <v>202</v>
+      </c>
+      <c r="C15" s="29"/>
+      <c r="D15" s="29"/>
+      <c r="E15" s="29"/>
+      <c r="F15" s="29"/>
+      <c r="G15" s="29"/>
+      <c r="H15" s="29"/>
+      <c r="I15" s="29"/>
+      <c r="J15" s="29"/>
+    </row>
+    <row r="16" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+      <c r="A16" s="24"/>
+      <c r="B16" s="27"/>
+      <c r="C16" s="27"/>
+      <c r="D16" s="27"/>
+      <c r="E16" s="27"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="27"/>
+      <c r="H16" s="27"/>
+      <c r="I16" s="27"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A17" s="23" t="s">
+        <v>203</v>
+      </c>
+      <c r="B17" s="23"/>
+      <c r="C17" s="27"/>
+      <c r="D17" s="27"/>
+      <c r="E17" s="27"/>
+      <c r="F17" s="27"/>
+      <c r="G17" s="27"/>
+      <c r="H17" s="27"/>
+      <c r="I17" s="27"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A18" s="25"/>
+      <c r="B18" s="23" t="s">
+        <v>204</v>
+      </c>
+      <c r="C18" s="23"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="23"/>
+      <c r="F18" s="23"/>
+      <c r="G18" s="23"/>
+      <c r="H18" s="23"/>
+      <c r="I18" s="23"/>
+      <c r="J18" s="23"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A19" s="25"/>
+      <c r="B19" s="26" t="s">
+        <v>205</v>
+      </c>
+      <c r="C19" s="26"/>
+      <c r="D19" s="26"/>
+      <c r="E19" s="26"/>
+      <c r="F19" s="26"/>
+      <c r="G19" s="26"/>
+      <c r="H19" s="26"/>
+      <c r="I19" s="26"/>
+      <c r="J19" s="26"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A20" s="25"/>
+      <c r="B20" s="26" t="s">
+        <v>206</v>
+      </c>
+      <c r="C20" s="26"/>
+      <c r="D20" s="26"/>
+      <c r="E20" s="26"/>
+      <c r="F20" s="26"/>
+      <c r="G20" s="26"/>
+      <c r="H20" s="26"/>
+      <c r="I20" s="26"/>
+      <c r="J20" s="26"/>
+    </row>
+    <row r="21" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+      <c r="A21" s="24"/>
+      <c r="B21" s="27"/>
+      <c r="C21" s="27"/>
+      <c r="D21" s="27"/>
+      <c r="E21" s="27"/>
+      <c r="F21" s="27"/>
+      <c r="G21" s="27"/>
+      <c r="H21" s="27"/>
+      <c r="I21" s="27"/>
+    </row>
+    <row r="22" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+      <c r="A22" s="24"/>
+      <c r="B22" s="27"/>
+      <c r="C22" s="27"/>
+      <c r="D22" s="27"/>
+      <c r="E22" s="27"/>
+      <c r="F22" s="27"/>
+      <c r="G22" s="27"/>
+      <c r="H22" s="27"/>
+      <c r="I22" s="27"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A23" s="25" t="s">
+        <v>207</v>
+      </c>
+      <c r="B23" s="25"/>
+      <c r="C23" s="25"/>
+      <c r="D23" s="27"/>
+      <c r="E23" s="27"/>
+      <c r="F23" s="27"/>
+      <c r="G23" s="27"/>
+      <c r="H23" s="27"/>
+      <c r="I23" s="27"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A24" s="25"/>
+      <c r="B24" s="25" t="s">
+        <v>208</v>
+      </c>
+      <c r="C24" s="25"/>
+      <c r="D24" s="25"/>
+      <c r="E24" s="25"/>
+      <c r="F24" s="25"/>
+      <c r="G24" s="25"/>
+      <c r="H24" s="25"/>
+      <c r="I24" s="25"/>
+      <c r="J24" s="25"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A25" s="25"/>
+      <c r="B25" s="28" t="s">
+        <v>209</v>
+      </c>
+      <c r="C25" s="28"/>
+      <c r="D25" s="28"/>
+      <c r="E25" s="28"/>
+      <c r="F25" s="28"/>
+      <c r="G25" s="28"/>
+      <c r="H25" s="28"/>
+      <c r="I25" s="28"/>
+      <c r="J25" s="28"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A26" s="25"/>
+      <c r="B26" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="C26" s="28"/>
+      <c r="D26" s="28"/>
+      <c r="E26" s="28"/>
+      <c r="F26" s="28"/>
+      <c r="G26" s="28"/>
+      <c r="H26" s="28"/>
+      <c r="I26" s="28"/>
+      <c r="J26" s="28"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B27" s="29" t="s">
+        <v>211</v>
+      </c>
+      <c r="C27" s="29"/>
+      <c r="D27" s="29"/>
+      <c r="E27" s="29"/>
+      <c r="F27" s="29"/>
+      <c r="G27" s="29"/>
+      <c r="H27" s="29"/>
+      <c r="I27" s="29"/>
+      <c r="J27" s="29"/>
+    </row>
+    <row r="28" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+      <c r="A28" s="24"/>
+      <c r="B28" s="27"/>
+      <c r="C28" s="27"/>
+      <c r="D28" s="27"/>
+      <c r="E28" s="27"/>
+      <c r="F28" s="27"/>
+      <c r="G28" s="27"/>
+      <c r="H28" s="27"/>
+      <c r="I28" s="27"/>
+    </row>
+    <row r="29" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+      <c r="A29" s="24"/>
+      <c r="B29" s="27"/>
+      <c r="C29" s="27"/>
+      <c r="D29" s="27"/>
+      <c r="E29" s="27"/>
+      <c r="F29" s="27"/>
+      <c r="G29" s="27"/>
+      <c r="H29" s="27"/>
+      <c r="I29" s="27"/>
+    </row>
+    <row r="30" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+      <c r="A30" s="30" t="s">
+        <v>212</v>
+      </c>
+      <c r="B30" s="30"/>
+      <c r="C30" s="30"/>
+      <c r="D30" s="30"/>
+      <c r="E30" s="24"/>
+      <c r="F30" s="24"/>
+      <c r="G30" s="24"/>
+      <c r="H30" s="24"/>
+      <c r="I30" s="24"/>
+    </row>
+    <row r="31" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+      <c r="A31" s="24"/>
+      <c r="B31" s="31" t="s">
+        <v>213</v>
+      </c>
+      <c r="C31" s="31"/>
+      <c r="D31" s="31"/>
+      <c r="E31" s="31"/>
+      <c r="F31" s="31"/>
+      <c r="G31" s="31"/>
+      <c r="H31" s="31"/>
+      <c r="I31" s="31"/>
+      <c r="J31" s="31"/>
+    </row>
+    <row r="32" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+      <c r="A32" s="24"/>
+      <c r="B32" s="32" t="s">
+        <v>214</v>
+      </c>
+      <c r="C32" s="32"/>
+      <c r="D32" s="32"/>
+      <c r="E32" s="32"/>
+      <c r="F32" s="32"/>
+      <c r="G32" s="32"/>
+      <c r="H32" s="32"/>
+      <c r="I32" s="32"/>
+      <c r="J32" s="32"/>
+    </row>
+    <row r="33" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+      <c r="A33" s="24"/>
+      <c r="B33" s="33"/>
+      <c r="C33" s="33"/>
+      <c r="D33" s="24"/>
+      <c r="E33" s="24"/>
+      <c r="F33" s="24"/>
+      <c r="G33" s="24"/>
+      <c r="H33" s="24"/>
+      <c r="I33" s="24"/>
+    </row>
+    <row r="35" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+      <c r="A35" s="23" t="s">
+        <v>215</v>
+      </c>
+      <c r="B35" s="23"/>
+      <c r="C35" s="23"/>
+      <c r="D35" s="24"/>
+      <c r="E35" s="24"/>
+      <c r="F35" s="24"/>
+      <c r="G35" s="24"/>
+      <c r="H35" s="24"/>
+      <c r="I35" s="24"/>
+    </row>
+    <row r="36" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+      <c r="A36" s="24"/>
+      <c r="B36" s="34" t="s">
+        <v>216</v>
+      </c>
+      <c r="C36" s="34"/>
+      <c r="D36" s="34"/>
+      <c r="E36" s="34"/>
+      <c r="F36" s="34"/>
+      <c r="G36" s="34"/>
+      <c r="H36" s="34"/>
+      <c r="I36" s="34"/>
+      <c r="J36" s="34"/>
+    </row>
+    <row r="37" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+      <c r="A37" s="24"/>
+      <c r="B37" s="26" t="s">
+        <v>217</v>
+      </c>
+      <c r="C37" s="26"/>
+      <c r="D37" s="26"/>
+      <c r="E37" s="26"/>
+      <c r="F37" s="26"/>
+      <c r="G37" s="26"/>
+      <c r="H37" s="26"/>
+      <c r="I37" s="26"/>
+      <c r="J37" s="26"/>
+    </row>
+    <row r="38" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+      <c r="A38" s="24"/>
+      <c r="B38" s="28"/>
+      <c r="C38" s="28"/>
+      <c r="D38" s="28"/>
+      <c r="E38" s="28"/>
+      <c r="F38" s="24"/>
+      <c r="G38" s="24"/>
+      <c r="H38" s="24"/>
+      <c r="I38" s="24"/>
+    </row>
+    <row r="40" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+      <c r="A40" s="23" t="s">
+        <v>218</v>
+      </c>
+      <c r="B40" s="23"/>
+      <c r="C40" s="24"/>
+      <c r="D40" s="24"/>
+      <c r="E40" s="24"/>
+      <c r="F40" s="24"/>
+      <c r="G40" s="24"/>
+      <c r="H40" s="24"/>
+      <c r="I40" s="24"/>
+    </row>
+    <row r="41" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+      <c r="A41" s="24"/>
+      <c r="B41" s="23" t="s">
+        <v>219</v>
+      </c>
+      <c r="C41" s="23"/>
+      <c r="D41" s="23"/>
+      <c r="E41" s="23"/>
+      <c r="F41" s="23"/>
+      <c r="G41" s="23"/>
+      <c r="H41" s="24"/>
+      <c r="I41" s="24"/>
+    </row>
+    <row r="42" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+      <c r="A42" s="24"/>
+      <c r="B42" s="25"/>
+      <c r="C42" s="25"/>
+      <c r="D42" s="25"/>
+      <c r="E42" s="25"/>
+      <c r="F42" s="24"/>
+      <c r="G42" s="24"/>
+      <c r="H42" s="24"/>
+      <c r="I42" s="24"/>
+    </row>
+    <row r="43" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+      <c r="A43" s="24"/>
+      <c r="B43" s="26" t="s">
+        <v>220</v>
+      </c>
+      <c r="C43" s="26"/>
+      <c r="D43" s="26"/>
+      <c r="E43" s="26"/>
+      <c r="F43" s="26"/>
+      <c r="G43" s="26"/>
+      <c r="H43" s="26"/>
+      <c r="I43" s="26"/>
+      <c r="J43" s="26"/>
+    </row>
+    <row r="44" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+      <c r="A44" s="24"/>
+      <c r="B44" s="26" t="s">
+        <v>221</v>
+      </c>
+      <c r="C44" s="26"/>
+      <c r="D44" s="26"/>
+      <c r="E44" s="26"/>
+      <c r="F44" s="26"/>
+      <c r="G44" s="26"/>
+      <c r="H44" s="26"/>
+      <c r="I44" s="26"/>
+      <c r="J44" s="26"/>
+    </row>
+    <row r="45" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+      <c r="A45" s="24"/>
+      <c r="B45" s="26" t="s">
+        <v>222</v>
+      </c>
+      <c r="C45" s="26"/>
+      <c r="D45" s="26"/>
+      <c r="E45" s="26"/>
+      <c r="F45" s="26"/>
+      <c r="G45" s="26"/>
+      <c r="H45" s="26"/>
+      <c r="I45" s="26"/>
+      <c r="J45" s="26"/>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B46" s="35"/>
+      <c r="C46" s="35"/>
+      <c r="D46" s="35"/>
+      <c r="E46" s="35"/>
+      <c r="F46" s="35"/>
+      <c r="G46" s="35"/>
+      <c r="H46" s="35"/>
+      <c r="I46" s="35"/>
+      <c r="J46" s="35"/>
+    </row>
+  </sheetData>
+  <mergeCells count="21">
+    <mergeCell ref="B44:J44"/>
+    <mergeCell ref="B45:J45"/>
+    <mergeCell ref="B46:J46"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="B36:J36"/>
+    <mergeCell ref="B37:J37"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="B41:G41"/>
+    <mergeCell ref="B43:J43"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="B18:J18"/>
+    <mergeCell ref="B19:J19"/>
+    <mergeCell ref="B20:J20"/>
+    <mergeCell ref="B31:J31"/>
+    <mergeCell ref="B32:J32"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="B3:I3"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="B7:J7"/>
+    <mergeCell ref="B8:J8"/>
+    <mergeCell ref="B9:J9"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45D248F1-3AEE-1A45-A3F2-BA8C8C115944}">
   <dimension ref="A1:J80"/>

--- a/data/crime/PR_Crime_Summary_2010_2025.xlsx
+++ b/data/crime/PR_Crime_Summary_2010_2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/venettov/Documents/Capstone/CAPSTONE_DATA_SCIENCE_RIVERARUIZ/data/crime/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D851435F-3A25-C442-8F95-4F808BE47722}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F195FA5-54A2-BB45-B7AC-5FBE4D1C3F3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="34560" windowHeight="21660" xr2:uid="{43E4E03C-6A79-7E4D-A8F1-AF00C31A2DE9}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="34560" windowHeight="21660" activeTab="16" xr2:uid="{43E4E03C-6A79-7E4D-A8F1-AF00C31A2DE9}"/>
   </bookViews>
   <sheets>
     <sheet name="2025" sheetId="1" r:id="rId1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1460" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1461" uniqueCount="224">
   <si>
     <t>Totales</t>
   </si>
@@ -1093,6 +1093,9 @@
   <si>
     <t>Se debe incluir el llevarse un vehículo sin permiso del dueño para realizar paseos alocados.</t>
   </si>
+  <si>
+    <t>Data from: Statistics_Institute_of_Puerto_Rico</t>
+  </si>
 </sst>
 </file>
 
@@ -1290,27 +1293,27 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1659,7 +1662,7 @@
     <col min="7" max="7" width="8.83203125" style="5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.5" style="5" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="18.83203125" style="5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.6640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.5" style="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
@@ -6267,7 +6270,7 @@
         <v>895</v>
       </c>
       <c r="J66">
-        <f t="shared" ref="J66:J97" si="2">SUM(B66:I66)</f>
+        <f t="shared" ref="J66:J79" si="2">SUM(B66:I66)</f>
         <v>7943</v>
       </c>
     </row>
@@ -9018,7 +9021,7 @@
         <v>952</v>
       </c>
       <c r="J66">
-        <f t="shared" ref="J66:J97" si="2">SUM(B66:I66)</f>
+        <f t="shared" ref="J66:J79" si="2">SUM(B66:I66)</f>
         <v>8368</v>
       </c>
     </row>
@@ -11489,7 +11492,7 @@
         <v>1140</v>
       </c>
       <c r="I66">
-        <f t="shared" ref="I66:I97" si="2">SUM(B66:H66)</f>
+        <f t="shared" ref="I66:I79" si="2">SUM(B66:H66)</f>
         <v>9567</v>
       </c>
     </row>
@@ -13916,7 +13919,7 @@
         <v>1283</v>
       </c>
       <c r="I66">
-        <f t="shared" ref="I66:I97" si="2">SUM(B66:H66)</f>
+        <f t="shared" ref="I66:I79" si="2">SUM(B66:H66)</f>
         <v>10464</v>
       </c>
     </row>
@@ -16859,35 +16862,35 @@
         <v>156</v>
       </c>
       <c r="B80" s="20">
-        <f>SUM(B2:B79)</f>
+        <f t="shared" ref="B80:I80" si="3">SUM(B2:B79)</f>
         <v>978</v>
       </c>
       <c r="C80" s="20">
-        <f>SUM(C2:C79)</f>
+        <f t="shared" si="3"/>
         <v>32</v>
       </c>
       <c r="D80" s="20">
-        <f>SUM(D2:D79)</f>
+        <f t="shared" si="3"/>
         <v>6298</v>
       </c>
       <c r="E80" s="20">
-        <f>SUM(E2:E79)</f>
+        <f t="shared" si="3"/>
         <v>2733</v>
       </c>
       <c r="F80" s="20">
-        <f>SUM(F2:F79)</f>
+        <f t="shared" si="3"/>
         <v>15287</v>
       </c>
       <c r="G80" s="20">
-        <f>SUM(G2:G79)</f>
+        <f t="shared" si="3"/>
         <v>30545</v>
       </c>
       <c r="H80" s="20">
-        <f>SUM(H2:H79)</f>
+        <f t="shared" si="3"/>
         <v>5847</v>
       </c>
       <c r="I80" s="20">
-        <f>SUM(I2:I79)</f>
+        <f t="shared" si="3"/>
         <v>61720</v>
       </c>
     </row>
@@ -19286,35 +19289,35 @@
         <v>156</v>
       </c>
       <c r="B80" s="20">
-        <f>SUM(B2:B79)</f>
+        <f t="shared" ref="B80:I80" si="3">SUM(B2:B79)</f>
         <v>1136</v>
       </c>
       <c r="C80" s="20">
-        <f>SUM(C2:C79)</f>
+        <f t="shared" si="3"/>
         <v>45</v>
       </c>
       <c r="D80" s="20">
-        <f>SUM(D2:D79)</f>
+        <f t="shared" si="3"/>
         <v>6465</v>
       </c>
       <c r="E80" s="20">
-        <f>SUM(E2:E79)</f>
+        <f t="shared" si="3"/>
         <v>2894</v>
       </c>
       <c r="F80" s="20">
-        <f>SUM(F2:F79)</f>
+        <f t="shared" si="3"/>
         <v>16591</v>
       </c>
       <c r="G80" s="20">
-        <f>SUM(G2:G79)</f>
+        <f t="shared" si="3"/>
         <v>29273</v>
       </c>
       <c r="H80" s="20">
-        <f>SUM(H2:H79)</f>
+        <f t="shared" si="3"/>
         <v>5853</v>
       </c>
       <c r="I80" s="20">
-        <f>SUM(I2:I79)</f>
+        <f t="shared" si="3"/>
         <v>62257</v>
       </c>
     </row>
@@ -21713,35 +21716,35 @@
         <v>156</v>
       </c>
       <c r="B80" s="20">
-        <f>SUM(B2:B79)</f>
+        <f t="shared" ref="B80:I80" si="3">SUM(B2:B79)</f>
         <v>983</v>
       </c>
       <c r="C80" s="20">
-        <f>SUM(C2:C79)</f>
+        <f t="shared" si="3"/>
         <v>39</v>
       </c>
       <c r="D80" s="20">
-        <f>SUM(D2:D79)</f>
+        <f t="shared" si="3"/>
         <v>6590</v>
       </c>
       <c r="E80" s="20">
-        <f>SUM(E2:E79)</f>
+        <f t="shared" si="3"/>
         <v>2753</v>
       </c>
       <c r="F80" s="20">
-        <f>SUM(F2:F79)</f>
+        <f t="shared" si="3"/>
         <v>17880</v>
       </c>
       <c r="G80" s="20">
-        <f>SUM(G2:G79)</f>
+        <f t="shared" si="3"/>
         <v>27182</v>
       </c>
       <c r="H80" s="20">
-        <f>SUM(H2:H79)</f>
+        <f t="shared" si="3"/>
         <v>6811</v>
       </c>
       <c r="I80" s="20">
-        <f>SUM(I2:I79)</f>
+        <f t="shared" si="3"/>
         <v>62238</v>
       </c>
     </row>
@@ -21869,7 +21872,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77629FE4-0AAF-4F45-8D35-1C3005808586}">
-  <dimension ref="A2:J46"/>
+  <dimension ref="A2:J49"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="17" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.5" style="22" customWidth="1"/>
@@ -22195,12 +22198,12 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="32" t="s">
         <v>192</v>
       </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
       <c r="E2" s="24"/>
       <c r="F2" s="24"/>
       <c r="G2" s="24"/>
@@ -22209,341 +22212,341 @@
     </row>
     <row r="3" spans="1:10" ht="18" x14ac:dyDescent="0.25">
       <c r="A3" s="24"/>
-      <c r="B3" s="23" t="s">
+      <c r="B3" s="32" t="s">
         <v>193</v>
       </c>
-      <c r="C3" s="23"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="23"/>
-      <c r="F3" s="23"/>
-      <c r="G3" s="23"/>
-      <c r="H3" s="23"/>
-      <c r="I3" s="23"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
     </row>
     <row r="4" spans="1:10" ht="18" x14ac:dyDescent="0.25">
       <c r="A4" s="24"/>
-      <c r="B4" s="25"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="25"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="25"/>
-      <c r="I4" s="25"/>
+      <c r="B4" s="23"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="32" t="s">
         <v>194</v>
       </c>
-      <c r="B6" s="23"/>
-      <c r="C6" s="23"/>
+      <c r="B6" s="32"/>
+      <c r="C6" s="32"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A7" s="25"/>
-      <c r="B7" s="23" t="s">
+      <c r="A7" s="23"/>
+      <c r="B7" s="32" t="s">
         <v>195</v>
       </c>
-      <c r="C7" s="23"/>
-      <c r="D7" s="23"/>
-      <c r="E7" s="23"/>
-      <c r="F7" s="23"/>
-      <c r="G7" s="23"/>
-      <c r="H7" s="23"/>
-      <c r="I7" s="23"/>
-      <c r="J7" s="23"/>
+      <c r="C7" s="32"/>
+      <c r="D7" s="32"/>
+      <c r="E7" s="32"/>
+      <c r="F7" s="32"/>
+      <c r="G7" s="32"/>
+      <c r="H7" s="32"/>
+      <c r="I7" s="32"/>
+      <c r="J7" s="32"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A8" s="25"/>
-      <c r="B8" s="26" t="s">
+      <c r="A8" s="23"/>
+      <c r="B8" s="30" t="s">
         <v>196</v>
       </c>
-      <c r="C8" s="26"/>
-      <c r="D8" s="26"/>
-      <c r="E8" s="26"/>
-      <c r="F8" s="26"/>
-      <c r="G8" s="26"/>
-      <c r="H8" s="26"/>
-      <c r="I8" s="26"/>
-      <c r="J8" s="26"/>
+      <c r="C8" s="30"/>
+      <c r="D8" s="30"/>
+      <c r="E8" s="30"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="30"/>
+      <c r="H8" s="30"/>
+      <c r="I8" s="30"/>
+      <c r="J8" s="30"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A9" s="25"/>
-      <c r="B9" s="26" t="s">
+      <c r="A9" s="23"/>
+      <c r="B9" s="30" t="s">
         <v>197</v>
       </c>
-      <c r="C9" s="26"/>
-      <c r="D9" s="26"/>
-      <c r="E9" s="26"/>
-      <c r="F9" s="26"/>
-      <c r="G9" s="26"/>
-      <c r="H9" s="26"/>
-      <c r="I9" s="26"/>
-      <c r="J9" s="26"/>
+      <c r="C9" s="30"/>
+      <c r="D9" s="30"/>
+      <c r="E9" s="30"/>
+      <c r="F9" s="30"/>
+      <c r="G9" s="30"/>
+      <c r="H9" s="30"/>
+      <c r="I9" s="30"/>
+      <c r="J9" s="30"/>
     </row>
     <row r="10" spans="1:10" ht="18" x14ac:dyDescent="0.25">
       <c r="A10" s="24"/>
-      <c r="B10" s="27"/>
-      <c r="C10" s="27"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="27"/>
-      <c r="F10" s="27"/>
-      <c r="G10" s="27"/>
-      <c r="H10" s="27"/>
-      <c r="I10" s="27"/>
+      <c r="B10" s="26"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="26"/>
+      <c r="I10" s="26"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A11" s="25" t="s">
+      <c r="A11" s="23" t="s">
         <v>198</v>
       </c>
-      <c r="B11" s="25"/>
-      <c r="C11" s="25"/>
-      <c r="D11" s="27"/>
-      <c r="E11" s="27"/>
-      <c r="F11" s="27"/>
-      <c r="G11" s="27"/>
-      <c r="H11" s="27"/>
-      <c r="I11" s="27"/>
+      <c r="B11" s="23"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="26"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="26"/>
+      <c r="G11" s="26"/>
+      <c r="H11" s="26"/>
+      <c r="I11" s="26"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A12" s="28"/>
-      <c r="B12" s="25" t="s">
+      <c r="A12" s="25"/>
+      <c r="B12" s="23" t="s">
         <v>199</v>
       </c>
-      <c r="C12" s="28"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="28"/>
-      <c r="F12" s="28"/>
-      <c r="G12" s="28"/>
-      <c r="H12" s="28"/>
-      <c r="I12" s="28"/>
-      <c r="J12" s="28"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="25"/>
+      <c r="F12" s="25"/>
+      <c r="G12" s="25"/>
+      <c r="H12" s="25"/>
+      <c r="I12" s="25"/>
+      <c r="J12" s="25"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A13" s="25"/>
-      <c r="B13" s="28" t="s">
+      <c r="A13" s="23"/>
+      <c r="B13" s="25" t="s">
         <v>200</v>
       </c>
-      <c r="C13" s="28"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="28"/>
-      <c r="F13" s="28"/>
-      <c r="G13" s="28"/>
-      <c r="H13" s="28"/>
-      <c r="I13" s="28"/>
-      <c r="J13" s="28"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="25"/>
+      <c r="F13" s="25"/>
+      <c r="G13" s="25"/>
+      <c r="H13" s="25"/>
+      <c r="I13" s="25"/>
+      <c r="J13" s="25"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A14" s="25"/>
-      <c r="B14" s="28" t="s">
+      <c r="A14" s="23"/>
+      <c r="B14" s="25" t="s">
         <v>201</v>
       </c>
-      <c r="C14" s="28"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="28"/>
-      <c r="F14" s="28"/>
-      <c r="G14" s="28"/>
-      <c r="H14" s="28"/>
-      <c r="I14" s="28"/>
-      <c r="J14" s="28"/>
+      <c r="C14" s="25"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="25"/>
+      <c r="F14" s="25"/>
+      <c r="G14" s="25"/>
+      <c r="H14" s="25"/>
+      <c r="I14" s="25"/>
+      <c r="J14" s="25"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B15" s="29" t="s">
+      <c r="B15" s="27" t="s">
         <v>202</v>
       </c>
-      <c r="C15" s="29"/>
-      <c r="D15" s="29"/>
-      <c r="E15" s="29"/>
-      <c r="F15" s="29"/>
-      <c r="G15" s="29"/>
-      <c r="H15" s="29"/>
-      <c r="I15" s="29"/>
-      <c r="J15" s="29"/>
+      <c r="C15" s="27"/>
+      <c r="D15" s="27"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="27"/>
+      <c r="G15" s="27"/>
+      <c r="H15" s="27"/>
+      <c r="I15" s="27"/>
+      <c r="J15" s="27"/>
     </row>
     <row r="16" spans="1:10" ht="18" x14ac:dyDescent="0.25">
       <c r="A16" s="24"/>
-      <c r="B16" s="27"/>
-      <c r="C16" s="27"/>
-      <c r="D16" s="27"/>
-      <c r="E16" s="27"/>
-      <c r="F16" s="27"/>
-      <c r="G16" s="27"/>
-      <c r="H16" s="27"/>
-      <c r="I16" s="27"/>
+      <c r="B16" s="26"/>
+      <c r="C16" s="26"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="26"/>
+      <c r="G16" s="26"/>
+      <c r="H16" s="26"/>
+      <c r="I16" s="26"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A17" s="23" t="s">
+      <c r="A17" s="32" t="s">
         <v>203</v>
       </c>
-      <c r="B17" s="23"/>
-      <c r="C17" s="27"/>
-      <c r="D17" s="27"/>
-      <c r="E17" s="27"/>
-      <c r="F17" s="27"/>
-      <c r="G17" s="27"/>
-      <c r="H17" s="27"/>
-      <c r="I17" s="27"/>
+      <c r="B17" s="32"/>
+      <c r="C17" s="26"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="26"/>
+      <c r="F17" s="26"/>
+      <c r="G17" s="26"/>
+      <c r="H17" s="26"/>
+      <c r="I17" s="26"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A18" s="25"/>
-      <c r="B18" s="23" t="s">
+      <c r="A18" s="23"/>
+      <c r="B18" s="32" t="s">
         <v>204</v>
       </c>
-      <c r="C18" s="23"/>
-      <c r="D18" s="23"/>
-      <c r="E18" s="23"/>
-      <c r="F18" s="23"/>
-      <c r="G18" s="23"/>
-      <c r="H18" s="23"/>
-      <c r="I18" s="23"/>
-      <c r="J18" s="23"/>
+      <c r="C18" s="32"/>
+      <c r="D18" s="32"/>
+      <c r="E18" s="32"/>
+      <c r="F18" s="32"/>
+      <c r="G18" s="32"/>
+      <c r="H18" s="32"/>
+      <c r="I18" s="32"/>
+      <c r="J18" s="32"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A19" s="25"/>
-      <c r="B19" s="26" t="s">
+      <c r="A19" s="23"/>
+      <c r="B19" s="30" t="s">
         <v>205</v>
       </c>
-      <c r="C19" s="26"/>
-      <c r="D19" s="26"/>
-      <c r="E19" s="26"/>
-      <c r="F19" s="26"/>
-      <c r="G19" s="26"/>
-      <c r="H19" s="26"/>
-      <c r="I19" s="26"/>
-      <c r="J19" s="26"/>
+      <c r="C19" s="30"/>
+      <c r="D19" s="30"/>
+      <c r="E19" s="30"/>
+      <c r="F19" s="30"/>
+      <c r="G19" s="30"/>
+      <c r="H19" s="30"/>
+      <c r="I19" s="30"/>
+      <c r="J19" s="30"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A20" s="25"/>
-      <c r="B20" s="26" t="s">
+      <c r="A20" s="23"/>
+      <c r="B20" s="30" t="s">
         <v>206</v>
       </c>
-      <c r="C20" s="26"/>
-      <c r="D20" s="26"/>
-      <c r="E20" s="26"/>
-      <c r="F20" s="26"/>
-      <c r="G20" s="26"/>
-      <c r="H20" s="26"/>
-      <c r="I20" s="26"/>
-      <c r="J20" s="26"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="30"/>
+      <c r="F20" s="30"/>
+      <c r="G20" s="30"/>
+      <c r="H20" s="30"/>
+      <c r="I20" s="30"/>
+      <c r="J20" s="30"/>
     </row>
     <row r="21" spans="1:10" ht="18" x14ac:dyDescent="0.25">
       <c r="A21" s="24"/>
-      <c r="B21" s="27"/>
-      <c r="C21" s="27"/>
-      <c r="D21" s="27"/>
-      <c r="E21" s="27"/>
-      <c r="F21" s="27"/>
-      <c r="G21" s="27"/>
-      <c r="H21" s="27"/>
-      <c r="I21" s="27"/>
+      <c r="B21" s="26"/>
+      <c r="C21" s="26"/>
+      <c r="D21" s="26"/>
+      <c r="E21" s="26"/>
+      <c r="F21" s="26"/>
+      <c r="G21" s="26"/>
+      <c r="H21" s="26"/>
+      <c r="I21" s="26"/>
     </row>
     <row r="22" spans="1:10" ht="18" x14ac:dyDescent="0.25">
       <c r="A22" s="24"/>
-      <c r="B22" s="27"/>
-      <c r="C22" s="27"/>
-      <c r="D22" s="27"/>
-      <c r="E22" s="27"/>
-      <c r="F22" s="27"/>
-      <c r="G22" s="27"/>
-      <c r="H22" s="27"/>
-      <c r="I22" s="27"/>
+      <c r="B22" s="26"/>
+      <c r="C22" s="26"/>
+      <c r="D22" s="26"/>
+      <c r="E22" s="26"/>
+      <c r="F22" s="26"/>
+      <c r="G22" s="26"/>
+      <c r="H22" s="26"/>
+      <c r="I22" s="26"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A23" s="25" t="s">
+      <c r="A23" s="23" t="s">
         <v>207</v>
       </c>
-      <c r="B23" s="25"/>
-      <c r="C23" s="25"/>
-      <c r="D23" s="27"/>
-      <c r="E23" s="27"/>
-      <c r="F23" s="27"/>
-      <c r="G23" s="27"/>
-      <c r="H23" s="27"/>
-      <c r="I23" s="27"/>
+      <c r="B23" s="23"/>
+      <c r="C23" s="23"/>
+      <c r="D23" s="26"/>
+      <c r="E23" s="26"/>
+      <c r="F23" s="26"/>
+      <c r="G23" s="26"/>
+      <c r="H23" s="26"/>
+      <c r="I23" s="26"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A24" s="25"/>
-      <c r="B24" s="25" t="s">
+      <c r="A24" s="23"/>
+      <c r="B24" s="23" t="s">
         <v>208</v>
       </c>
-      <c r="C24" s="25"/>
-      <c r="D24" s="25"/>
-      <c r="E24" s="25"/>
-      <c r="F24" s="25"/>
-      <c r="G24" s="25"/>
-      <c r="H24" s="25"/>
-      <c r="I24" s="25"/>
-      <c r="J24" s="25"/>
+      <c r="C24" s="23"/>
+      <c r="D24" s="23"/>
+      <c r="E24" s="23"/>
+      <c r="F24" s="23"/>
+      <c r="G24" s="23"/>
+      <c r="H24" s="23"/>
+      <c r="I24" s="23"/>
+      <c r="J24" s="23"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A25" s="25"/>
-      <c r="B25" s="28" t="s">
+      <c r="A25" s="23"/>
+      <c r="B25" s="25" t="s">
         <v>209</v>
       </c>
-      <c r="C25" s="28"/>
-      <c r="D25" s="28"/>
-      <c r="E25" s="28"/>
-      <c r="F25" s="28"/>
-      <c r="G25" s="28"/>
-      <c r="H25" s="28"/>
-      <c r="I25" s="28"/>
-      <c r="J25" s="28"/>
+      <c r="C25" s="25"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="25"/>
+      <c r="F25" s="25"/>
+      <c r="G25" s="25"/>
+      <c r="H25" s="25"/>
+      <c r="I25" s="25"/>
+      <c r="J25" s="25"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A26" s="25"/>
-      <c r="B26" s="28" t="s">
+      <c r="A26" s="23"/>
+      <c r="B26" s="25" t="s">
         <v>210</v>
       </c>
-      <c r="C26" s="28"/>
-      <c r="D26" s="28"/>
-      <c r="E26" s="28"/>
-      <c r="F26" s="28"/>
-      <c r="G26" s="28"/>
-      <c r="H26" s="28"/>
-      <c r="I26" s="28"/>
-      <c r="J26" s="28"/>
+      <c r="C26" s="25"/>
+      <c r="D26" s="25"/>
+      <c r="E26" s="25"/>
+      <c r="F26" s="25"/>
+      <c r="G26" s="25"/>
+      <c r="H26" s="25"/>
+      <c r="I26" s="25"/>
+      <c r="J26" s="25"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B27" s="29" t="s">
+      <c r="B27" s="27" t="s">
         <v>211</v>
       </c>
-      <c r="C27" s="29"/>
-      <c r="D27" s="29"/>
-      <c r="E27" s="29"/>
-      <c r="F27" s="29"/>
-      <c r="G27" s="29"/>
-      <c r="H27" s="29"/>
-      <c r="I27" s="29"/>
-      <c r="J27" s="29"/>
+      <c r="C27" s="27"/>
+      <c r="D27" s="27"/>
+      <c r="E27" s="27"/>
+      <c r="F27" s="27"/>
+      <c r="G27" s="27"/>
+      <c r="H27" s="27"/>
+      <c r="I27" s="27"/>
+      <c r="J27" s="27"/>
     </row>
     <row r="28" spans="1:10" ht="18" x14ac:dyDescent="0.25">
       <c r="A28" s="24"/>
-      <c r="B28" s="27"/>
-      <c r="C28" s="27"/>
-      <c r="D28" s="27"/>
-      <c r="E28" s="27"/>
-      <c r="F28" s="27"/>
-      <c r="G28" s="27"/>
-      <c r="H28" s="27"/>
-      <c r="I28" s="27"/>
+      <c r="B28" s="26"/>
+      <c r="C28" s="26"/>
+      <c r="D28" s="26"/>
+      <c r="E28" s="26"/>
+      <c r="F28" s="26"/>
+      <c r="G28" s="26"/>
+      <c r="H28" s="26"/>
+      <c r="I28" s="26"/>
     </row>
     <row r="29" spans="1:10" ht="18" x14ac:dyDescent="0.25">
       <c r="A29" s="24"/>
-      <c r="B29" s="27"/>
-      <c r="C29" s="27"/>
-      <c r="D29" s="27"/>
-      <c r="E29" s="27"/>
-      <c r="F29" s="27"/>
-      <c r="G29" s="27"/>
-      <c r="H29" s="27"/>
-      <c r="I29" s="27"/>
+      <c r="B29" s="26"/>
+      <c r="C29" s="26"/>
+      <c r="D29" s="26"/>
+      <c r="E29" s="26"/>
+      <c r="F29" s="26"/>
+      <c r="G29" s="26"/>
+      <c r="H29" s="26"/>
+      <c r="I29" s="26"/>
     </row>
     <row r="30" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A30" s="30" t="s">
+      <c r="A30" s="28" t="s">
         <v>212</v>
       </c>
-      <c r="B30" s="30"/>
-      <c r="C30" s="30"/>
-      <c r="D30" s="30"/>
+      <c r="B30" s="28"/>
+      <c r="C30" s="28"/>
+      <c r="D30" s="28"/>
       <c r="E30" s="24"/>
       <c r="F30" s="24"/>
       <c r="G30" s="24"/>
@@ -22552,36 +22555,36 @@
     </row>
     <row r="31" spans="1:10" ht="18" x14ac:dyDescent="0.25">
       <c r="A31" s="24"/>
-      <c r="B31" s="31" t="s">
+      <c r="B31" s="34" t="s">
         <v>213</v>
       </c>
-      <c r="C31" s="31"/>
-      <c r="D31" s="31"/>
-      <c r="E31" s="31"/>
-      <c r="F31" s="31"/>
-      <c r="G31" s="31"/>
-      <c r="H31" s="31"/>
-      <c r="I31" s="31"/>
-      <c r="J31" s="31"/>
+      <c r="C31" s="34"/>
+      <c r="D31" s="34"/>
+      <c r="E31" s="34"/>
+      <c r="F31" s="34"/>
+      <c r="G31" s="34"/>
+      <c r="H31" s="34"/>
+      <c r="I31" s="34"/>
+      <c r="J31" s="34"/>
     </row>
     <row r="32" spans="1:10" ht="18" x14ac:dyDescent="0.25">
       <c r="A32" s="24"/>
-      <c r="B32" s="32" t="s">
+      <c r="B32" s="35" t="s">
         <v>214</v>
       </c>
-      <c r="C32" s="32"/>
-      <c r="D32" s="32"/>
-      <c r="E32" s="32"/>
-      <c r="F32" s="32"/>
-      <c r="G32" s="32"/>
-      <c r="H32" s="32"/>
-      <c r="I32" s="32"/>
-      <c r="J32" s="32"/>
+      <c r="C32" s="35"/>
+      <c r="D32" s="35"/>
+      <c r="E32" s="35"/>
+      <c r="F32" s="35"/>
+      <c r="G32" s="35"/>
+      <c r="H32" s="35"/>
+      <c r="I32" s="35"/>
+      <c r="J32" s="35"/>
     </row>
     <row r="33" spans="1:10" ht="18" x14ac:dyDescent="0.25">
       <c r="A33" s="24"/>
-      <c r="B33" s="33"/>
-      <c r="C33" s="33"/>
+      <c r="B33" s="29"/>
+      <c r="C33" s="29"/>
       <c r="D33" s="24"/>
       <c r="E33" s="24"/>
       <c r="F33" s="24"/>
@@ -22590,11 +22593,11 @@
       <c r="I33" s="24"/>
     </row>
     <row r="35" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A35" s="23" t="s">
+      <c r="A35" s="32" t="s">
         <v>215</v>
       </c>
-      <c r="B35" s="23"/>
-      <c r="C35" s="23"/>
+      <c r="B35" s="32"/>
+      <c r="C35" s="32"/>
       <c r="D35" s="24"/>
       <c r="E35" s="24"/>
       <c r="F35" s="24"/>
@@ -22604,48 +22607,48 @@
     </row>
     <row r="36" spans="1:10" ht="18" x14ac:dyDescent="0.25">
       <c r="A36" s="24"/>
-      <c r="B36" s="34" t="s">
+      <c r="B36" s="33" t="s">
         <v>216</v>
       </c>
-      <c r="C36" s="34"/>
-      <c r="D36" s="34"/>
-      <c r="E36" s="34"/>
-      <c r="F36" s="34"/>
-      <c r="G36" s="34"/>
-      <c r="H36" s="34"/>
-      <c r="I36" s="34"/>
-      <c r="J36" s="34"/>
+      <c r="C36" s="33"/>
+      <c r="D36" s="33"/>
+      <c r="E36" s="33"/>
+      <c r="F36" s="33"/>
+      <c r="G36" s="33"/>
+      <c r="H36" s="33"/>
+      <c r="I36" s="33"/>
+      <c r="J36" s="33"/>
     </row>
     <row r="37" spans="1:10" ht="18" x14ac:dyDescent="0.25">
       <c r="A37" s="24"/>
-      <c r="B37" s="26" t="s">
+      <c r="B37" s="30" t="s">
         <v>217</v>
       </c>
-      <c r="C37" s="26"/>
-      <c r="D37" s="26"/>
-      <c r="E37" s="26"/>
-      <c r="F37" s="26"/>
-      <c r="G37" s="26"/>
-      <c r="H37" s="26"/>
-      <c r="I37" s="26"/>
-      <c r="J37" s="26"/>
+      <c r="C37" s="30"/>
+      <c r="D37" s="30"/>
+      <c r="E37" s="30"/>
+      <c r="F37" s="30"/>
+      <c r="G37" s="30"/>
+      <c r="H37" s="30"/>
+      <c r="I37" s="30"/>
+      <c r="J37" s="30"/>
     </row>
     <row r="38" spans="1:10" ht="18" x14ac:dyDescent="0.25">
       <c r="A38" s="24"/>
-      <c r="B38" s="28"/>
-      <c r="C38" s="28"/>
-      <c r="D38" s="28"/>
-      <c r="E38" s="28"/>
+      <c r="B38" s="25"/>
+      <c r="C38" s="25"/>
+      <c r="D38" s="25"/>
+      <c r="E38" s="25"/>
       <c r="F38" s="24"/>
       <c r="G38" s="24"/>
       <c r="H38" s="24"/>
       <c r="I38" s="24"/>
     </row>
     <row r="40" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A40" s="23" t="s">
+      <c r="A40" s="32" t="s">
         <v>218</v>
       </c>
-      <c r="B40" s="23"/>
+      <c r="B40" s="32"/>
       <c r="C40" s="24"/>
       <c r="D40" s="24"/>
       <c r="E40" s="24"/>
@@ -22656,23 +22659,23 @@
     </row>
     <row r="41" spans="1:10" ht="18" x14ac:dyDescent="0.25">
       <c r="A41" s="24"/>
-      <c r="B41" s="23" t="s">
+      <c r="B41" s="32" t="s">
         <v>219</v>
       </c>
-      <c r="C41" s="23"/>
-      <c r="D41" s="23"/>
-      <c r="E41" s="23"/>
-      <c r="F41" s="23"/>
-      <c r="G41" s="23"/>
+      <c r="C41" s="32"/>
+      <c r="D41" s="32"/>
+      <c r="E41" s="32"/>
+      <c r="F41" s="32"/>
+      <c r="G41" s="32"/>
       <c r="H41" s="24"/>
       <c r="I41" s="24"/>
     </row>
     <row r="42" spans="1:10" ht="18" x14ac:dyDescent="0.25">
       <c r="A42" s="24"/>
-      <c r="B42" s="25"/>
-      <c r="C42" s="25"/>
-      <c r="D42" s="25"/>
-      <c r="E42" s="25"/>
+      <c r="B42" s="23"/>
+      <c r="C42" s="23"/>
+      <c r="D42" s="23"/>
+      <c r="E42" s="23"/>
       <c r="F42" s="24"/>
       <c r="G42" s="24"/>
       <c r="H42" s="24"/>
@@ -22680,59 +22683,76 @@
     </row>
     <row r="43" spans="1:10" ht="18" x14ac:dyDescent="0.25">
       <c r="A43" s="24"/>
-      <c r="B43" s="26" t="s">
+      <c r="B43" s="30" t="s">
         <v>220</v>
       </c>
-      <c r="C43" s="26"/>
-      <c r="D43" s="26"/>
-      <c r="E43" s="26"/>
-      <c r="F43" s="26"/>
-      <c r="G43" s="26"/>
-      <c r="H43" s="26"/>
-      <c r="I43" s="26"/>
-      <c r="J43" s="26"/>
+      <c r="C43" s="30"/>
+      <c r="D43" s="30"/>
+      <c r="E43" s="30"/>
+      <c r="F43" s="30"/>
+      <c r="G43" s="30"/>
+      <c r="H43" s="30"/>
+      <c r="I43" s="30"/>
+      <c r="J43" s="30"/>
     </row>
     <row r="44" spans="1:10" ht="18" x14ac:dyDescent="0.25">
       <c r="A44" s="24"/>
-      <c r="B44" s="26" t="s">
+      <c r="B44" s="30" t="s">
         <v>221</v>
       </c>
-      <c r="C44" s="26"/>
-      <c r="D44" s="26"/>
-      <c r="E44" s="26"/>
-      <c r="F44" s="26"/>
-      <c r="G44" s="26"/>
-      <c r="H44" s="26"/>
-      <c r="I44" s="26"/>
-      <c r="J44" s="26"/>
+      <c r="C44" s="30"/>
+      <c r="D44" s="30"/>
+      <c r="E44" s="30"/>
+      <c r="F44" s="30"/>
+      <c r="G44" s="30"/>
+      <c r="H44" s="30"/>
+      <c r="I44" s="30"/>
+      <c r="J44" s="30"/>
     </row>
     <row r="45" spans="1:10" ht="18" x14ac:dyDescent="0.25">
       <c r="A45" s="24"/>
-      <c r="B45" s="26" t="s">
+      <c r="B45" s="30" t="s">
         <v>222</v>
       </c>
-      <c r="C45" s="26"/>
-      <c r="D45" s="26"/>
-      <c r="E45" s="26"/>
-      <c r="F45" s="26"/>
-      <c r="G45" s="26"/>
-      <c r="H45" s="26"/>
-      <c r="I45" s="26"/>
-      <c r="J45" s="26"/>
+      <c r="C45" s="30"/>
+      <c r="D45" s="30"/>
+      <c r="E45" s="30"/>
+      <c r="F45" s="30"/>
+      <c r="G45" s="30"/>
+      <c r="H45" s="30"/>
+      <c r="I45" s="30"/>
+      <c r="J45" s="30"/>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B46" s="35"/>
-      <c r="C46" s="35"/>
-      <c r="D46" s="35"/>
-      <c r="E46" s="35"/>
-      <c r="F46" s="35"/>
-      <c r="G46" s="35"/>
-      <c r="H46" s="35"/>
-      <c r="I46" s="35"/>
-      <c r="J46" s="35"/>
+      <c r="B46" s="31"/>
+      <c r="C46" s="31"/>
+      <c r="D46" s="31"/>
+      <c r="E46" s="31"/>
+      <c r="F46" s="31"/>
+      <c r="G46" s="31"/>
+      <c r="H46" s="31"/>
+      <c r="I46" s="31"/>
+      <c r="J46" s="31"/>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A49" s="22" t="s">
+        <v>223</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="B32:J32"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="B3:I3"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="B7:J7"/>
+    <mergeCell ref="B8:J8"/>
+    <mergeCell ref="B9:J9"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="B18:J18"/>
+    <mergeCell ref="B19:J19"/>
+    <mergeCell ref="B20:J20"/>
+    <mergeCell ref="B31:J31"/>
     <mergeCell ref="B44:J44"/>
     <mergeCell ref="B45:J45"/>
     <mergeCell ref="B46:J46"/>
@@ -22742,18 +22762,6 @@
     <mergeCell ref="A40:B40"/>
     <mergeCell ref="B41:G41"/>
     <mergeCell ref="B43:J43"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="B18:J18"/>
-    <mergeCell ref="B19:J19"/>
-    <mergeCell ref="B20:J20"/>
-    <mergeCell ref="B31:J31"/>
-    <mergeCell ref="B32:J32"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="B3:I3"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="B7:J7"/>
-    <mergeCell ref="B8:J8"/>
-    <mergeCell ref="B9:J9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -30795,7 +30803,7 @@
         <v>957</v>
       </c>
       <c r="J66">
-        <f t="shared" ref="J66:J97" si="2">SUM(B66:I66)</f>
+        <f t="shared" ref="J66:J79" si="2">SUM(B66:I66)</f>
         <v>4851</v>
       </c>
     </row>
@@ -33842,7 +33850,7 @@
         <v>800</v>
       </c>
       <c r="J66">
-        <f t="shared" ref="J66:J97" si="2">SUM(B66:I66)</f>
+        <f t="shared" ref="J66:J79" si="2">SUM(B66:I66)</f>
         <v>3897</v>
       </c>
     </row>
@@ -36764,7 +36772,7 @@
         <v>604</v>
       </c>
       <c r="J66">
-        <f t="shared" ref="J66:J97" si="2">SUM(B66:I66)</f>
+        <f t="shared" ref="J66:J79" si="2">SUM(B66:I66)</f>
         <v>3751</v>
       </c>
     </row>
@@ -39686,7 +39694,7 @@
         <v>1133</v>
       </c>
       <c r="J66">
-        <f t="shared" ref="J66:J97" si="2">SUM(B66:I66)</f>
+        <f t="shared" ref="J66:J79" si="2">SUM(B66:I66)</f>
         <v>6042</v>
       </c>
     </row>
@@ -42608,7 +42616,7 @@
         <v>1139</v>
       </c>
       <c r="J66">
-        <f t="shared" ref="J66:J97" si="2">SUM(B66:I66)</f>
+        <f t="shared" ref="J66:J79" si="2">SUM(B66:I66)</f>
         <v>6837</v>
       </c>
     </row>
@@ -45200,7 +45208,7 @@
         <v>788</v>
       </c>
       <c r="J66">
-        <f t="shared" ref="J66:J97" si="2">SUM(B66:I66)</f>
+        <f t="shared" ref="J66:J80" si="2">SUM(B66:I66)</f>
         <v>6952</v>
       </c>
     </row>

--- a/data/crime/PR_Crime_Summary_2010_2025.xlsx
+++ b/data/crime/PR_Crime_Summary_2010_2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10102"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/venettov/Documents/Capstone/CAPSTONE_DATA_SCIENCE_RIVERARUIZ/data/crime/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andreruiz/Documents/Capstone/CAPSTONE_DATA_SCIENCE_RIVERARUIZ/data/crime/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F195FA5-54A2-BB45-B7AC-5FBE4D1C3F3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4A423A7-22E6-2F43-A760-2A72A5957F35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="34560" windowHeight="21660" activeTab="16" xr2:uid="{43E4E03C-6A79-7E4D-A8F1-AF00C31A2DE9}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="21460" xr2:uid="{43E4E03C-6A79-7E4D-A8F1-AF00C31A2DE9}"/>
   </bookViews>
   <sheets>
     <sheet name="2025" sheetId="1" r:id="rId1"/>
@@ -1302,18 +1302,18 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -22198,12 +22198,12 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="31" t="s">
         <v>192</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
       <c r="E2" s="24"/>
       <c r="F2" s="24"/>
       <c r="G2" s="24"/>
@@ -22212,16 +22212,16 @@
     </row>
     <row r="3" spans="1:10" ht="18" x14ac:dyDescent="0.25">
       <c r="A3" s="24"/>
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="31" t="s">
         <v>193</v>
       </c>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
-      <c r="G3" s="32"/>
-      <c r="H3" s="32"/>
-      <c r="I3" s="32"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
     </row>
     <row r="4" spans="1:10" ht="18" x14ac:dyDescent="0.25">
       <c r="A4" s="24"/>
@@ -22235,53 +22235,53 @@
       <c r="I4" s="23"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A6" s="32" t="s">
+      <c r="A6" s="31" t="s">
         <v>194</v>
       </c>
-      <c r="B6" s="32"/>
-      <c r="C6" s="32"/>
+      <c r="B6" s="31"/>
+      <c r="C6" s="31"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="23"/>
-      <c r="B7" s="32" t="s">
+      <c r="B7" s="31" t="s">
         <v>195</v>
       </c>
-      <c r="C7" s="32"/>
-      <c r="D7" s="32"/>
-      <c r="E7" s="32"/>
-      <c r="F7" s="32"/>
-      <c r="G7" s="32"/>
-      <c r="H7" s="32"/>
-      <c r="I7" s="32"/>
-      <c r="J7" s="32"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="31"/>
+      <c r="F7" s="31"/>
+      <c r="G7" s="31"/>
+      <c r="H7" s="31"/>
+      <c r="I7" s="31"/>
+      <c r="J7" s="31"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="23"/>
-      <c r="B8" s="30" t="s">
+      <c r="B8" s="32" t="s">
         <v>196</v>
       </c>
-      <c r="C8" s="30"/>
-      <c r="D8" s="30"/>
-      <c r="E8" s="30"/>
-      <c r="F8" s="30"/>
-      <c r="G8" s="30"/>
-      <c r="H8" s="30"/>
-      <c r="I8" s="30"/>
-      <c r="J8" s="30"/>
+      <c r="C8" s="32"/>
+      <c r="D8" s="32"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="32"/>
+      <c r="G8" s="32"/>
+      <c r="H8" s="32"/>
+      <c r="I8" s="32"/>
+      <c r="J8" s="32"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="23"/>
-      <c r="B9" s="30" t="s">
+      <c r="B9" s="32" t="s">
         <v>197</v>
       </c>
-      <c r="C9" s="30"/>
-      <c r="D9" s="30"/>
-      <c r="E9" s="30"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="30"/>
-      <c r="H9" s="30"/>
-      <c r="I9" s="30"/>
-      <c r="J9" s="30"/>
+      <c r="C9" s="32"/>
+      <c r="D9" s="32"/>
+      <c r="E9" s="32"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="32"/>
+      <c r="H9" s="32"/>
+      <c r="I9" s="32"/>
+      <c r="J9" s="32"/>
     </row>
     <row r="10" spans="1:10" ht="18" x14ac:dyDescent="0.25">
       <c r="A10" s="24"/>
@@ -22374,10 +22374,10 @@
       <c r="I16" s="26"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A17" s="32" t="s">
+      <c r="A17" s="31" t="s">
         <v>203</v>
       </c>
-      <c r="B17" s="32"/>
+      <c r="B17" s="31"/>
       <c r="C17" s="26"/>
       <c r="D17" s="26"/>
       <c r="E17" s="26"/>
@@ -22388,45 +22388,45 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" s="23"/>
-      <c r="B18" s="32" t="s">
+      <c r="B18" s="31" t="s">
         <v>204</v>
       </c>
-      <c r="C18" s="32"/>
-      <c r="D18" s="32"/>
-      <c r="E18" s="32"/>
-      <c r="F18" s="32"/>
-      <c r="G18" s="32"/>
-      <c r="H18" s="32"/>
-      <c r="I18" s="32"/>
-      <c r="J18" s="32"/>
+      <c r="C18" s="31"/>
+      <c r="D18" s="31"/>
+      <c r="E18" s="31"/>
+      <c r="F18" s="31"/>
+      <c r="G18" s="31"/>
+      <c r="H18" s="31"/>
+      <c r="I18" s="31"/>
+      <c r="J18" s="31"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" s="23"/>
-      <c r="B19" s="30" t="s">
+      <c r="B19" s="32" t="s">
         <v>205</v>
       </c>
-      <c r="C19" s="30"/>
-      <c r="D19" s="30"/>
-      <c r="E19" s="30"/>
-      <c r="F19" s="30"/>
-      <c r="G19" s="30"/>
-      <c r="H19" s="30"/>
-      <c r="I19" s="30"/>
-      <c r="J19" s="30"/>
+      <c r="C19" s="32"/>
+      <c r="D19" s="32"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="32"/>
+      <c r="G19" s="32"/>
+      <c r="H19" s="32"/>
+      <c r="I19" s="32"/>
+      <c r="J19" s="32"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" s="23"/>
-      <c r="B20" s="30" t="s">
+      <c r="B20" s="32" t="s">
         <v>206</v>
       </c>
-      <c r="C20" s="30"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="30"/>
-      <c r="F20" s="30"/>
-      <c r="G20" s="30"/>
-      <c r="H20" s="30"/>
-      <c r="I20" s="30"/>
-      <c r="J20" s="30"/>
+      <c r="C20" s="32"/>
+      <c r="D20" s="32"/>
+      <c r="E20" s="32"/>
+      <c r="F20" s="32"/>
+      <c r="G20" s="32"/>
+      <c r="H20" s="32"/>
+      <c r="I20" s="32"/>
+      <c r="J20" s="32"/>
     </row>
     <row r="21" spans="1:10" ht="18" x14ac:dyDescent="0.25">
       <c r="A21" s="24"/>
@@ -22555,31 +22555,31 @@
     </row>
     <row r="31" spans="1:10" ht="18" x14ac:dyDescent="0.25">
       <c r="A31" s="24"/>
-      <c r="B31" s="34" t="s">
+      <c r="B31" s="33" t="s">
         <v>213</v>
       </c>
-      <c r="C31" s="34"/>
-      <c r="D31" s="34"/>
-      <c r="E31" s="34"/>
-      <c r="F31" s="34"/>
-      <c r="G31" s="34"/>
-      <c r="H31" s="34"/>
-      <c r="I31" s="34"/>
-      <c r="J31" s="34"/>
+      <c r="C31" s="33"/>
+      <c r="D31" s="33"/>
+      <c r="E31" s="33"/>
+      <c r="F31" s="33"/>
+      <c r="G31" s="33"/>
+      <c r="H31" s="33"/>
+      <c r="I31" s="33"/>
+      <c r="J31" s="33"/>
     </row>
     <row r="32" spans="1:10" ht="18" x14ac:dyDescent="0.25">
       <c r="A32" s="24"/>
-      <c r="B32" s="35" t="s">
+      <c r="B32" s="30" t="s">
         <v>214</v>
       </c>
-      <c r="C32" s="35"/>
-      <c r="D32" s="35"/>
-      <c r="E32" s="35"/>
-      <c r="F32" s="35"/>
-      <c r="G32" s="35"/>
-      <c r="H32" s="35"/>
-      <c r="I32" s="35"/>
-      <c r="J32" s="35"/>
+      <c r="C32" s="30"/>
+      <c r="D32" s="30"/>
+      <c r="E32" s="30"/>
+      <c r="F32" s="30"/>
+      <c r="G32" s="30"/>
+      <c r="H32" s="30"/>
+      <c r="I32" s="30"/>
+      <c r="J32" s="30"/>
     </row>
     <row r="33" spans="1:10" ht="18" x14ac:dyDescent="0.25">
       <c r="A33" s="24"/>
@@ -22593,11 +22593,11 @@
       <c r="I33" s="24"/>
     </row>
     <row r="35" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A35" s="32" t="s">
+      <c r="A35" s="31" t="s">
         <v>215</v>
       </c>
-      <c r="B35" s="32"/>
-      <c r="C35" s="32"/>
+      <c r="B35" s="31"/>
+      <c r="C35" s="31"/>
       <c r="D35" s="24"/>
       <c r="E35" s="24"/>
       <c r="F35" s="24"/>
@@ -22607,31 +22607,31 @@
     </row>
     <row r="36" spans="1:10" ht="18" x14ac:dyDescent="0.25">
       <c r="A36" s="24"/>
-      <c r="B36" s="33" t="s">
+      <c r="B36" s="35" t="s">
         <v>216</v>
       </c>
-      <c r="C36" s="33"/>
-      <c r="D36" s="33"/>
-      <c r="E36" s="33"/>
-      <c r="F36" s="33"/>
-      <c r="G36" s="33"/>
-      <c r="H36" s="33"/>
-      <c r="I36" s="33"/>
-      <c r="J36" s="33"/>
+      <c r="C36" s="35"/>
+      <c r="D36" s="35"/>
+      <c r="E36" s="35"/>
+      <c r="F36" s="35"/>
+      <c r="G36" s="35"/>
+      <c r="H36" s="35"/>
+      <c r="I36" s="35"/>
+      <c r="J36" s="35"/>
     </row>
     <row r="37" spans="1:10" ht="18" x14ac:dyDescent="0.25">
       <c r="A37" s="24"/>
-      <c r="B37" s="30" t="s">
+      <c r="B37" s="32" t="s">
         <v>217</v>
       </c>
-      <c r="C37" s="30"/>
-      <c r="D37" s="30"/>
-      <c r="E37" s="30"/>
-      <c r="F37" s="30"/>
-      <c r="G37" s="30"/>
-      <c r="H37" s="30"/>
-      <c r="I37" s="30"/>
-      <c r="J37" s="30"/>
+      <c r="C37" s="32"/>
+      <c r="D37" s="32"/>
+      <c r="E37" s="32"/>
+      <c r="F37" s="32"/>
+      <c r="G37" s="32"/>
+      <c r="H37" s="32"/>
+      <c r="I37" s="32"/>
+      <c r="J37" s="32"/>
     </row>
     <row r="38" spans="1:10" ht="18" x14ac:dyDescent="0.25">
       <c r="A38" s="24"/>
@@ -22645,10 +22645,10 @@
       <c r="I38" s="24"/>
     </row>
     <row r="40" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A40" s="32" t="s">
+      <c r="A40" s="31" t="s">
         <v>218</v>
       </c>
-      <c r="B40" s="32"/>
+      <c r="B40" s="31"/>
       <c r="C40" s="24"/>
       <c r="D40" s="24"/>
       <c r="E40" s="24"/>
@@ -22659,14 +22659,14 @@
     </row>
     <row r="41" spans="1:10" ht="18" x14ac:dyDescent="0.25">
       <c r="A41" s="24"/>
-      <c r="B41" s="32" t="s">
+      <c r="B41" s="31" t="s">
         <v>219</v>
       </c>
-      <c r="C41" s="32"/>
-      <c r="D41" s="32"/>
-      <c r="E41" s="32"/>
-      <c r="F41" s="32"/>
-      <c r="G41" s="32"/>
+      <c r="C41" s="31"/>
+      <c r="D41" s="31"/>
+      <c r="E41" s="31"/>
+      <c r="F41" s="31"/>
+      <c r="G41" s="31"/>
       <c r="H41" s="24"/>
       <c r="I41" s="24"/>
     </row>
@@ -22683,56 +22683,56 @@
     </row>
     <row r="43" spans="1:10" ht="18" x14ac:dyDescent="0.25">
       <c r="A43" s="24"/>
-      <c r="B43" s="30" t="s">
+      <c r="B43" s="32" t="s">
         <v>220</v>
       </c>
-      <c r="C43" s="30"/>
-      <c r="D43" s="30"/>
-      <c r="E43" s="30"/>
-      <c r="F43" s="30"/>
-      <c r="G43" s="30"/>
-      <c r="H43" s="30"/>
-      <c r="I43" s="30"/>
-      <c r="J43" s="30"/>
+      <c r="C43" s="32"/>
+      <c r="D43" s="32"/>
+      <c r="E43" s="32"/>
+      <c r="F43" s="32"/>
+      <c r="G43" s="32"/>
+      <c r="H43" s="32"/>
+      <c r="I43" s="32"/>
+      <c r="J43" s="32"/>
     </row>
     <row r="44" spans="1:10" ht="18" x14ac:dyDescent="0.25">
       <c r="A44" s="24"/>
-      <c r="B44" s="30" t="s">
+      <c r="B44" s="32" t="s">
         <v>221</v>
       </c>
-      <c r="C44" s="30"/>
-      <c r="D44" s="30"/>
-      <c r="E44" s="30"/>
-      <c r="F44" s="30"/>
-      <c r="G44" s="30"/>
-      <c r="H44" s="30"/>
-      <c r="I44" s="30"/>
-      <c r="J44" s="30"/>
+      <c r="C44" s="32"/>
+      <c r="D44" s="32"/>
+      <c r="E44" s="32"/>
+      <c r="F44" s="32"/>
+      <c r="G44" s="32"/>
+      <c r="H44" s="32"/>
+      <c r="I44" s="32"/>
+      <c r="J44" s="32"/>
     </row>
     <row r="45" spans="1:10" ht="18" x14ac:dyDescent="0.25">
       <c r="A45" s="24"/>
-      <c r="B45" s="30" t="s">
+      <c r="B45" s="32" t="s">
         <v>222</v>
       </c>
-      <c r="C45" s="30"/>
-      <c r="D45" s="30"/>
-      <c r="E45" s="30"/>
-      <c r="F45" s="30"/>
-      <c r="G45" s="30"/>
-      <c r="H45" s="30"/>
-      <c r="I45" s="30"/>
-      <c r="J45" s="30"/>
+      <c r="C45" s="32"/>
+      <c r="D45" s="32"/>
+      <c r="E45" s="32"/>
+      <c r="F45" s="32"/>
+      <c r="G45" s="32"/>
+      <c r="H45" s="32"/>
+      <c r="I45" s="32"/>
+      <c r="J45" s="32"/>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B46" s="31"/>
-      <c r="C46" s="31"/>
-      <c r="D46" s="31"/>
-      <c r="E46" s="31"/>
-      <c r="F46" s="31"/>
-      <c r="G46" s="31"/>
-      <c r="H46" s="31"/>
-      <c r="I46" s="31"/>
-      <c r="J46" s="31"/>
+      <c r="B46" s="34"/>
+      <c r="C46" s="34"/>
+      <c r="D46" s="34"/>
+      <c r="E46" s="34"/>
+      <c r="F46" s="34"/>
+      <c r="G46" s="34"/>
+      <c r="H46" s="34"/>
+      <c r="I46" s="34"/>
+      <c r="J46" s="34"/>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A49" s="22" t="s">
@@ -22741,6 +22741,15 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="B44:J44"/>
+    <mergeCell ref="B45:J45"/>
+    <mergeCell ref="B46:J46"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="B36:J36"/>
+    <mergeCell ref="B37:J37"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="B41:G41"/>
+    <mergeCell ref="B43:J43"/>
     <mergeCell ref="B32:J32"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="B3:I3"/>
@@ -22753,15 +22762,6 @@
     <mergeCell ref="B19:J19"/>
     <mergeCell ref="B20:J20"/>
     <mergeCell ref="B31:J31"/>
-    <mergeCell ref="B44:J44"/>
-    <mergeCell ref="B45:J45"/>
-    <mergeCell ref="B46:J46"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="B36:J36"/>
-    <mergeCell ref="B37:J37"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="B41:G41"/>
-    <mergeCell ref="B43:J43"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
